--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
@@ -36634,7 +36634,9 @@
       <c r="AH18" s="7" t="n"/>
       <c r="AI18" s="7" t="n"/>
       <c r="AJ18" s="7" t="n"/>
-      <c r="AK18" s="5" t="n"/>
+      <c r="AK18" s="5" t="n">
+        <v>362</v>
+      </c>
       <c r="AL18" s="5" t="n">
         <v>10</v>
       </c>
@@ -39164,9 +39166,13 @@
       <c r="X36" s="15" t="n">
         <v>0.00233</v>
       </c>
-      <c r="Y36" s="5" t="n"/>
+      <c r="Y36" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="Z36" s="7" t="n"/>
-      <c r="AA36" s="7" t="n"/>
+      <c r="AA36" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="AB36" s="7" t="n"/>
       <c r="AC36" s="7" t="n"/>
       <c r="AD36" s="7" t="n"/>
@@ -39174,7 +39180,9 @@
       <c r="AF36" s="7" t="n"/>
       <c r="AG36" s="7" t="n"/>
       <c r="AH36" s="7" t="n"/>
-      <c r="AI36" s="7" t="n"/>
+      <c r="AI36" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="AJ36" s="7" t="n"/>
       <c r="AK36" s="5" t="n">
         <v>331</v>
@@ -39189,9 +39197,11 @@
         <v>1</v>
       </c>
       <c r="AO36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AP36" s="2" t="n"/>
       <c r="AQ36" s="2" t="n">
         <v>0</v>
       </c>
@@ -40004,15 +40014,23 @@
         <v>41.6</v>
       </c>
       <c r="X42" s="15" t="n"/>
-      <c r="Y42" s="5" t="n"/>
+      <c r="Y42" s="5" t="n">
+        <v>29</v>
+      </c>
       <c r="Z42" s="7" t="n"/>
       <c r="AA42" s="7" t="n"/>
-      <c r="AB42" s="7" t="n"/>
+      <c r="AB42" s="7" t="n">
+        <v>38</v>
+      </c>
       <c r="AC42" s="7" t="n"/>
       <c r="AD42" s="7" t="n"/>
       <c r="AE42" s="7" t="n"/>
-      <c r="AF42" s="7" t="n"/>
-      <c r="AG42" s="7" t="n"/>
+      <c r="AF42" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG42" s="7" t="n">
+        <v>35</v>
+      </c>
       <c r="AH42" s="7" t="n"/>
       <c r="AI42" s="7" t="n"/>
       <c r="AJ42" s="7" t="n"/>
@@ -40025,9 +40043,11 @@
         <v>0</v>
       </c>
       <c r="AO42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AP42" s="2" t="n"/>
       <c r="AQ42" s="2" t="n">
         <v>0</v>
       </c>
@@ -41199,15 +41219,23 @@
       <c r="X51" s="15" t="n">
         <v>0.03043</v>
       </c>
-      <c r="Y51" s="5" t="n"/>
+      <c r="Y51" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="Z51" s="7" t="n"/>
       <c r="AA51" s="7" t="n"/>
-      <c r="AB51" s="7" t="n"/>
+      <c r="AB51" s="7" t="n">
+        <v>36</v>
+      </c>
       <c r="AC51" s="7" t="n"/>
       <c r="AD51" s="7" t="n"/>
       <c r="AE51" s="7" t="n"/>
-      <c r="AF51" s="7" t="n"/>
-      <c r="AG51" s="7" t="n"/>
+      <c r="AF51" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG51" s="7" t="n">
+        <v>54</v>
+      </c>
       <c r="AH51" s="7" t="n"/>
       <c r="AI51" s="7" t="n"/>
       <c r="AJ51" s="7" t="n"/>
@@ -41222,9 +41250,11 @@
         <v>0</v>
       </c>
       <c r="AO51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AP51" s="2" t="n"/>
       <c r="AQ51" s="2" t="n">
         <v>0</v>
       </c>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regiao_painel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metropole_painel" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regiao_detalhe" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metropole_detalhe" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="regiao_painel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metropole_painel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="regiao_detalhe" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="metropole_detalhe" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="dados" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'regiao_painel'!$A$1:$S$8</definedName>
@@ -37111,12 +37111,8 @@
       <c r="M2" s="5" t="n">
         <v>768</v>
       </c>
-      <c r="N2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
       <c r="P2" s="5" t="n">
         <v>305</v>
       </c>
@@ -37262,9 +37258,7 @@
       <c r="L3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="5" t="n">
-        <v>3099</v>
-      </c>
+      <c r="M3" s="5" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="5" t="n">
@@ -37393,15 +37387,9 @@
       <c r="M4" s="5" t="n">
         <v>702</v>
       </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>1505</v>
-      </c>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n">
         <v>6058</v>
       </c>
@@ -37705,12 +37693,8 @@
       <c r="M6" s="5" t="n">
         <v>465</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
       <c r="P6" s="5" t="n">
         <v>747</v>
       </c>
@@ -37864,15 +37848,9 @@
       <c r="L7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <v>6361</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
       <c r="P7" s="5" t="n">
         <v>162</v>
       </c>
@@ -38017,12 +37995,8 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n"/>
-      <c r="N8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
       <c r="P8" s="5" t="n">
         <v>5</v>
       </c>
@@ -38148,9 +38122,7 @@
       <c r="L9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="5" t="n">
-        <v>3702</v>
-      </c>
+      <c r="M9" s="5" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="5" t="n">
@@ -38414,18 +38386,10 @@
       <c r="L11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="5" t="n">
-        <v>5144</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>1138</v>
-      </c>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n">
         <v>27673</v>
       </c>
@@ -38571,12 +38535,8 @@
       <c r="M12" s="5" t="n">
         <v>387</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
       <c r="P12" s="5" t="n">
         <v>118</v>
       </c>
@@ -38727,12 +38687,8 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
       <c r="P13" s="5" t="n">
         <v>52</v>
       </c>
@@ -38761,7 +38717,7 @@
         <v>0.01614</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>25.5</v>
@@ -38773,7 +38729,7 @@
         <v>35</v>
       </c>
       <c r="AC13" s="7" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="AD13" s="7" t="n">
         <v>48</v>
@@ -38782,7 +38738,7 @@
         <v>54.5</v>
       </c>
       <c r="AF13" s="7" t="n">
-        <v>56.75</v>
+        <v>54.25</v>
       </c>
       <c r="AG13" s="7" t="n">
         <v>73.5</v>
@@ -38794,7 +38750,7 @@
         <v>40</v>
       </c>
       <c r="AJ13" s="7" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="AK13" s="7" t="n">
         <v>13</v>
@@ -38893,12 +38849,8 @@
       <c r="M14" s="5" t="n">
         <v>307</v>
       </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
       <c r="P14" s="5" t="n">
         <v>723</v>
       </c>
@@ -39038,15 +38990,9 @@
       <c r="L15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="5" t="n">
-        <v>1142</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
       <c r="P15" s="5" t="n">
         <v>105</v>
       </c>
@@ -39200,12 +39146,8 @@
       <c r="L16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="5" t="n">
-        <v>1201</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="5" t="n">
         <v>754</v>
@@ -39234,8 +39176,12 @@
       <c r="X16" s="15" t="n">
         <v>0.00134</v>
       </c>
-      <c r="Y16" s="5" t="n"/>
-      <c r="Z16" s="7" t="n"/>
+      <c r="Y16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="AA16" s="7" t="n"/>
       <c r="AB16" s="7" t="n"/>
       <c r="AC16" s="7" t="n"/>
@@ -39260,9 +39206,11 @@
         <v>0</v>
       </c>
       <c r="AR16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AT16" s="2" t="n">
         <v>0</v>
       </c>
@@ -39330,15 +39278,9 @@
       <c r="L17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="5" t="n">
-        <v>4984</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
       <c r="P17" s="5" t="n">
         <v>137</v>
       </c>
@@ -39486,15 +39428,9 @@
       <c r="L18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="5" t="n">
-        <v>3205</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
       <c r="P18" s="5" t="n">
         <v>391</v>
       </c>
@@ -39506,21 +39442,43 @@
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="15" t="n"/>
-      <c r="Y18" s="5" t="n"/>
-      <c r="Z18" s="7" t="n"/>
-      <c r="AA18" s="7" t="n"/>
-      <c r="AB18" s="7" t="n"/>
-      <c r="AC18" s="7" t="n"/>
-      <c r="AD18" s="7" t="n"/>
-      <c r="AE18" s="7" t="n"/>
-      <c r="AF18" s="7" t="n"/>
-      <c r="AG18" s="7" t="n"/>
-      <c r="AH18" s="7" t="n"/>
+      <c r="Y18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AA18" s="7" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AC18" s="7" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AD18" s="7" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AE18" s="7" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AF18" s="7" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="AG18" s="7" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AH18" s="7" t="n">
+        <v>102.05</v>
+      </c>
       <c r="AI18" s="7" t="n"/>
       <c r="AJ18" s="7" t="n"/>
       <c r="AK18" s="7" t="n"/>
       <c r="AL18" s="7" t="n"/>
-      <c r="AM18" s="7" t="n"/>
+      <c r="AM18" s="7" t="n">
+        <v>38.9</v>
+      </c>
       <c r="AN18" s="5" t="n">
         <v>362</v>
       </c>
@@ -39534,9 +39492,11 @@
         <v>0</v>
       </c>
       <c r="AR18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AT18" s="2" t="n">
         <v>0</v>
       </c>
@@ -39604,9 +39564,7 @@
       <c r="L19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="5" t="n">
-        <v>2556</v>
-      </c>
+      <c r="M19" s="5" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="5" t="n">
@@ -39798,8 +39756,12 @@
       <c r="X20" s="15" t="n">
         <v>0.00223</v>
       </c>
-      <c r="Y20" s="5" t="n"/>
-      <c r="Z20" s="7" t="n"/>
+      <c r="Y20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="AA20" s="7" t="n"/>
       <c r="AB20" s="7" t="n"/>
       <c r="AC20" s="7" t="n"/>
@@ -39824,9 +39786,11 @@
         <v>1</v>
       </c>
       <c r="AR20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AT20" s="2" t="n">
         <v>0</v>
       </c>
@@ -39897,12 +39861,8 @@
       <c r="M21" s="5" t="n">
         <v>302</v>
       </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
       <c r="P21" s="5" t="n">
         <v>576</v>
       </c>
@@ -40050,15 +40010,9 @@
       <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="5" t="n">
-        <v>1216</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
       <c r="P22" s="5" t="n">
         <v>312</v>
       </c>
@@ -40310,9 +40264,7 @@
       <c r="L24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="5" t="n">
-        <v>7638</v>
-      </c>
+      <c r="M24" s="5" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="5" t="n">
@@ -40336,21 +40288,43 @@
         <v>207.62</v>
       </c>
       <c r="X24" s="15" t="n"/>
-      <c r="Y24" s="5" t="n"/>
+      <c r="Y24" s="5" t="n">
+        <v>75</v>
+      </c>
       <c r="Z24" s="7" t="n"/>
-      <c r="AA24" s="7" t="n"/>
-      <c r="AB24" s="7" t="n"/>
-      <c r="AC24" s="7" t="n"/>
-      <c r="AD24" s="7" t="n"/>
-      <c r="AE24" s="7" t="n"/>
+      <c r="AA24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB24" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC24" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="AE24" s="7" t="n">
+        <v>75.75</v>
+      </c>
       <c r="AF24" s="7" t="n"/>
       <c r="AG24" s="7" t="n"/>
       <c r="AH24" s="7" t="n"/>
-      <c r="AI24" s="7" t="n"/>
-      <c r="AJ24" s="7" t="n"/>
-      <c r="AK24" s="7" t="n"/>
-      <c r="AL24" s="7" t="n"/>
-      <c r="AM24" s="7" t="n"/>
+      <c r="AI24" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="AJ24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM24" s="7" t="n">
+        <v>32</v>
+      </c>
       <c r="AN24" s="5" t="n">
         <v>1357</v>
       </c>
@@ -40360,9 +40334,11 @@
         <v>0</v>
       </c>
       <c r="AR24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AS24" s="2" t="n"/>
       <c r="AT24" s="2" t="n">
         <v>0</v>
       </c>
@@ -40433,15 +40409,9 @@
       <c r="M25" s="5" t="n">
         <v>351</v>
       </c>
-      <c r="N25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>1796</v>
-      </c>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n">
         <v>6682</v>
       </c>
@@ -40467,7 +40437,7 @@
         <v>0.00353</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="Z25" s="7" t="n">
         <v>12.5</v>
@@ -40476,28 +40446,28 @@
         <v>11</v>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>45</v>
+        <v>39.5</v>
       </c>
       <c r="AC25" s="7" t="n">
-        <v>46</v>
+        <v>43.25</v>
       </c>
       <c r="AD25" s="7" t="n">
-        <v>56</v>
+        <v>50.5</v>
       </c>
       <c r="AE25" s="7" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AF25" s="7" t="n">
-        <v>52.25</v>
+        <v>49.5</v>
       </c>
       <c r="AG25" s="7" t="n">
-        <v>68.5</v>
+        <v>63</v>
       </c>
       <c r="AH25" s="7" t="n">
-        <v>96.75</v>
+        <v>83.75</v>
       </c>
       <c r="AI25" s="7" t="n">
-        <v>52.5</v>
+        <v>42</v>
       </c>
       <c r="AJ25" s="7" t="n">
         <v>28.5</v>
@@ -40629,7 +40599,7 @@
         <v>0.00153</v>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Z26" s="7" t="n"/>
       <c r="AA26" s="7" t="n">
@@ -40645,7 +40615,7 @@
         <v>60</v>
       </c>
       <c r="AE26" s="7" t="n">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="AF26" s="7" t="n"/>
       <c r="AG26" s="7" t="n"/>
@@ -40657,7 +40627,7 @@
         <v>39</v>
       </c>
       <c r="AK26" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" s="7" t="n">
         <v>8</v>
@@ -40750,12 +40720,8 @@
       <c r="L27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="5" t="n">
-        <v>10228</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="5" t="n">
         <v>684</v>
@@ -40881,9 +40847,7 @@
       <c r="M28" s="5" t="n">
         <v>607</v>
       </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="5" t="n">
         <v>907</v>
@@ -41029,15 +40993,9 @@
       <c r="M29" s="5" t="n">
         <v>577</v>
       </c>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>1006</v>
-      </c>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n">
         <v>41545</v>
       </c>
@@ -41063,20 +41021,20 @@
         <v>0.00048</v>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Z29" s="7" t="n"/>
       <c r="AA29" s="7" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
       <c r="AB29" s="7" t="n">
         <v>43.4</v>
       </c>
       <c r="AC29" s="7" t="n">
-        <v>55.57</v>
+        <v>54.15</v>
       </c>
       <c r="AD29" s="7" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="AE29" s="7" t="n">
         <v>83.55</v>
@@ -41097,7 +41055,7 @@
         <v>9</v>
       </c>
       <c r="AM29" s="7" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="AN29" s="5" t="n">
         <v>225</v>
@@ -41217,7 +41175,7 @@
         <v>0.00419</v>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z30" s="7" t="n"/>
       <c r="AA30" s="7" t="n">
@@ -41227,7 +41185,7 @@
         <v>32</v>
       </c>
       <c r="AC30" s="7" t="n">
-        <v>47.75</v>
+        <v>47.5</v>
       </c>
       <c r="AD30" s="7" t="n">
         <v>60</v>
@@ -41242,7 +41200,7 @@
         <v>28</v>
       </c>
       <c r="AJ30" s="7" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AK30" s="7" t="n">
         <v>22</v>
@@ -41336,15 +41294,9 @@
       <c r="L31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="5" t="n">
-        <v>7180</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
       <c r="P31" s="5" t="n">
         <v>424</v>
       </c>
@@ -41494,18 +41446,10 @@
       <c r="L32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="5" t="n">
-        <v>16823</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>1993</v>
-      </c>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n">
         <v>2732</v>
       </c>
@@ -41655,9 +41599,7 @@
       <c r="M33" s="5" t="n">
         <v>687</v>
       </c>
-      <c r="N33" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="5" t="n">
         <v>835</v>
@@ -41803,15 +41745,9 @@
       <c r="M34" s="5" t="n">
         <v>628</v>
       </c>
-      <c r="N34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>1205</v>
-      </c>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n">
         <v>110000</v>
       </c>
@@ -41836,18 +41772,42 @@
       <c r="X34" s="15" t="n">
         <v>0.00117</v>
       </c>
-      <c r="Y34" s="5" t="n"/>
-      <c r="Z34" s="7" t="n"/>
-      <c r="AA34" s="7" t="n"/>
-      <c r="AB34" s="7" t="n"/>
-      <c r="AC34" s="7" t="n"/>
-      <c r="AD34" s="7" t="n"/>
-      <c r="AE34" s="7" t="n"/>
-      <c r="AF34" s="7" t="n"/>
-      <c r="AG34" s="7" t="n"/>
-      <c r="AH34" s="7" t="n"/>
-      <c r="AI34" s="7" t="n"/>
-      <c r="AJ34" s="7" t="n"/>
+      <c r="Y34" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z34" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA34" s="7" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AB34" s="7" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AC34" s="7" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="AD34" s="7" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AE34" s="7" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AF34" s="7" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="AG34" s="7" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AH34" s="7" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AI34" s="7" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AJ34" s="7" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AK34" s="7" t="n"/>
       <c r="AL34" s="7" t="n"/>
       <c r="AM34" s="7" t="n"/>
@@ -41862,9 +41822,11 @@
         <v>1</v>
       </c>
       <c r="AR34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS34" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AT34" s="2" t="n">
         <v>0</v>
       </c>
@@ -41935,9 +41897,7 @@
       <c r="M35" s="5" t="n">
         <v>435</v>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="5" t="n">
         <v>818</v>
@@ -42385,15 +42345,9 @@
       <c r="M38" s="5" t="n">
         <v>820</v>
       </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>1083</v>
-      </c>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n">
         <v>8510</v>
       </c>
@@ -42519,15 +42473,9 @@
       <c r="M39" s="5" t="n">
         <v>566</v>
       </c>
-      <c r="N39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>1744</v>
-      </c>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n">
         <v>23415</v>
       </c>
@@ -42650,9 +42598,7 @@
       <c r="L40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="5" t="n">
-        <v>4310</v>
-      </c>
+      <c r="M40" s="5" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="5" t="n">
@@ -42683,23 +42629,23 @@
         <v>0.0064</v>
       </c>
       <c r="Y40" s="5" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="Z40" s="7" t="n"/>
       <c r="AA40" s="7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AB40" s="7" t="n">
         <v>29</v>
       </c>
       <c r="AC40" s="7" t="n">
-        <v>18.18</v>
+        <v>17.9</v>
       </c>
       <c r="AD40" s="7" t="n">
-        <v>39.5</v>
+        <v>38</v>
       </c>
       <c r="AE40" s="7" t="n">
-        <v>53.5</v>
+        <v>52.72</v>
       </c>
       <c r="AF40" s="7" t="n"/>
       <c r="AG40" s="7" t="n"/>
@@ -42714,7 +42660,7 @@
         <v>13</v>
       </c>
       <c r="AL40" s="7" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="AM40" s="7" t="n"/>
       <c r="AN40" s="5" t="n">
@@ -42805,12 +42751,8 @@
       <c r="M41" s="5" t="n">
         <v>563</v>
       </c>
-      <c r="N41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
       <c r="P41" s="5" t="n">
         <v>484</v>
       </c>
@@ -42956,15 +42898,9 @@
       <c r="L42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="5" t="n">
-        <v>1527</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
       <c r="P42" s="5" t="n">
         <v>305</v>
       </c>
@@ -42989,7 +42925,7 @@
       </c>
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="5" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Z42" s="7" t="n"/>
       <c r="AA42" s="7" t="n"/>
@@ -43003,7 +42939,7 @@
       <c r="AG42" s="7" t="n"/>
       <c r="AH42" s="7" t="n"/>
       <c r="AI42" s="7" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ42" s="7" t="n">
         <v>35</v>
@@ -43095,15 +43031,9 @@
       <c r="M43" s="5" t="n">
         <v>364</v>
       </c>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>1486</v>
-      </c>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n">
         <v>34668</v>
       </c>
@@ -43225,9 +43155,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="5" t="n"/>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="5" t="n">
         <v>926</v>
@@ -43257,7 +43185,7 @@
         <v>0.00343</v>
       </c>
       <c r="Y44" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z44" s="7" t="n"/>
       <c r="AA44" s="7" t="n">
@@ -43373,9 +43301,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="5" t="n"/>
-      <c r="N45" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="5" t="n">
         <v>770</v>
@@ -43405,7 +43331,7 @@
         <v>0.00173</v>
       </c>
       <c r="Y45" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z45" s="7" t="n"/>
       <c r="AA45" s="7" t="n">
@@ -43415,13 +43341,13 @@
         <v>12</v>
       </c>
       <c r="AC45" s="7" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="AD45" s="7" t="n">
         <v>24</v>
       </c>
       <c r="AE45" s="7" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="AF45" s="7" t="n"/>
       <c r="AG45" s="7" t="n"/>
@@ -43519,15 +43445,9 @@
         <v>0</v>
       </c>
       <c r="M46" s="5" t="n"/>
-      <c r="N46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>1175</v>
-      </c>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n">
         <v>18698</v>
       </c>
@@ -43553,35 +43473,35 @@
         <v>0.00693</v>
       </c>
       <c r="Y46" s="5" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Z46" s="7" t="n"/>
       <c r="AA46" s="7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AB46" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC46" s="7" t="n">
-        <v>43</v>
+        <v>41.75</v>
       </c>
       <c r="AD46" s="7" t="n">
-        <v>47.5</v>
+        <v>44</v>
       </c>
       <c r="AE46" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF46" s="7" t="n"/>
       <c r="AG46" s="7" t="n"/>
       <c r="AH46" s="7" t="n"/>
       <c r="AI46" s="7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ46" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AK46" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL46" s="7" t="n">
         <v>8</v>
@@ -43673,15 +43593,9 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="n"/>
-      <c r="N47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v>1152</v>
-      </c>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n">
         <v>25555</v>
       </c>
@@ -43706,8 +43620,12 @@
       <c r="X47" s="15" t="n">
         <v>0.01197</v>
       </c>
-      <c r="Y47" s="5" t="n"/>
-      <c r="Z47" s="7" t="n"/>
+      <c r="Y47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="7" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA47" s="7" t="n"/>
       <c r="AB47" s="7" t="n"/>
       <c r="AC47" s="7" t="n"/>
@@ -43734,9 +43652,11 @@
         <v>0</v>
       </c>
       <c r="AR47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS47" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AT47" s="2" t="n">
         <v>0</v>
       </c>
@@ -44057,12 +43977,8 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n"/>
-      <c r="N50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
       <c r="P50" s="5" t="n">
         <v>590</v>
       </c>
@@ -44187,12 +44103,8 @@
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n"/>
-      <c r="N51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
       <c r="P51" s="5" t="n">
         <v>294</v>
       </c>
@@ -44221,7 +44133,7 @@
         <v>0.03043</v>
       </c>
       <c r="Y51" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="7" t="n"/>
       <c r="AA51" s="7" t="n"/>
@@ -44238,7 +44150,7 @@
         <v>36</v>
       </c>
       <c r="AJ51" s="7" t="n">
-        <v>54</v>
+        <v>44.5</v>
       </c>
       <c r="AK51" s="7" t="n"/>
       <c r="AL51" s="7" t="n"/>
@@ -44327,9 +44239,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="n"/>
-      <c r="N52" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="5" t="n">
         <v>834</v>
@@ -44355,7 +44265,7 @@
       <c r="W52" s="6" t="n"/>
       <c r="X52" s="15" t="n"/>
       <c r="Y52" s="5" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="Z52" s="7" t="n"/>
       <c r="AA52" s="7" t="n">
@@ -44365,13 +44275,13 @@
         <v>25.9</v>
       </c>
       <c r="AC52" s="7" t="n">
-        <v>28.4</v>
+        <v>30.4</v>
       </c>
       <c r="AD52" s="7" t="n">
         <v>32.7</v>
       </c>
       <c r="AE52" s="7" t="n">
-        <v>37.6</v>
+        <v>43.6</v>
       </c>
       <c r="AF52" s="7" t="n"/>
       <c r="AG52" s="7" t="n"/>
@@ -44471,15 +44381,9 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="n"/>
-      <c r="N53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v>1681</v>
-      </c>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n">
         <v>87929</v>
       </c>
@@ -44505,23 +44409,23 @@
         <v>0.0023</v>
       </c>
       <c r="Y53" s="5" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="Z53" s="7" t="n"/>
       <c r="AA53" s="7" t="n">
         <v>17.9</v>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="AC53" s="7" t="n">
-        <v>34.9</v>
+        <v>35.55</v>
       </c>
       <c r="AD53" s="7" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="AE53" s="7" t="n">
-        <v>67.67</v>
+        <v>71.42</v>
       </c>
       <c r="AF53" s="7" t="n"/>
       <c r="AG53" s="7" t="n"/>
@@ -44539,7 +44443,7 @@
         <v>6.75</v>
       </c>
       <c r="AM53" s="7" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="AN53" s="5" t="n"/>
       <c r="AO53" s="5" t="n">
@@ -44624,12 +44528,8 @@
       <c r="L54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
       <c r="P54" s="5" t="n">
         <v>591</v>
@@ -44659,7 +44559,7 @@
         <v>0.00084</v>
       </c>
       <c r="Y54" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Z54" s="7" t="n"/>
       <c r="AA54" s="7" t="n">
@@ -44669,13 +44569,13 @@
         <v>40</v>
       </c>
       <c r="AC54" s="7" t="n">
-        <v>52.75</v>
+        <v>55</v>
       </c>
       <c r="AD54" s="7" t="n">
         <v>65</v>
       </c>
       <c r="AE54" s="7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF54" s="7" t="n"/>
       <c r="AG54" s="7" t="n"/>
@@ -44687,7 +44587,7 @@
         <v>28</v>
       </c>
       <c r="AK54" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL54" s="7" t="n">
         <v>8</v>
@@ -44778,12 +44678,8 @@
       <c r="L55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="5" t="n">
-        <v>15504</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="5" t="n">
         <v>583</v>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
@@ -37725,9 +37725,7 @@
       <c r="Y6" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="Z6" s="7" t="n">
-        <v>30</v>
-      </c>
+      <c r="Z6" s="7" t="n"/>
       <c r="AA6" s="7" t="n">
         <v>9</v>
       </c>
@@ -37735,7 +37733,7 @@
         <v>31</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="AD6" s="7" t="n">
         <v>40</v>
@@ -37743,15 +37741,9 @@
       <c r="AE6" s="7" t="n">
         <v>46.75</v>
       </c>
-      <c r="AF6" s="7" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="AG6" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH6" s="7" t="n">
-        <v>76.75</v>
-      </c>
+      <c r="AF6" s="7" t="n"/>
+      <c r="AG6" s="7" t="n"/>
+      <c r="AH6" s="7" t="n"/>
       <c r="AI6" s="7" t="n"/>
       <c r="AJ6" s="7" t="n"/>
       <c r="AK6" s="7" t="n">
@@ -37779,7 +37771,7 @@
         <v>1</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="2" t="n">
         <v>0</v>
@@ -38415,9 +38407,11 @@
         <v>0.00249</v>
       </c>
       <c r="Y11" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z11" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="Z11" s="7" t="n"/>
       <c r="AA11" s="7" t="n">
         <v>12</v>
       </c>
@@ -38433,9 +38427,15 @@
       <c r="AE11" s="7" t="n">
         <v>37.5</v>
       </c>
-      <c r="AF11" s="7" t="n"/>
-      <c r="AG11" s="7" t="n"/>
-      <c r="AH11" s="7" t="n"/>
+      <c r="AF11" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG11" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH11" s="7" t="n">
+        <v>62.5</v>
+      </c>
       <c r="AI11" s="7" t="n">
         <v>34</v>
       </c>
@@ -38463,7 +38463,7 @@
         <v>1</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" s="2" t="n">
         <v>0</v>
@@ -38875,9 +38875,11 @@
       </c>
       <c r="X14" s="15" t="n"/>
       <c r="Y14" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z14" s="7" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="AA14" s="7" t="n">
         <v>20</v>
       </c>
@@ -38893,9 +38895,15 @@
       <c r="AE14" s="7" t="n">
         <v>71.5</v>
       </c>
-      <c r="AF14" s="7" t="n"/>
-      <c r="AG14" s="7" t="n"/>
-      <c r="AH14" s="7" t="n"/>
+      <c r="AF14" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG14" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="AH14" s="7" t="n">
+        <v>94</v>
+      </c>
       <c r="AI14" s="7" t="n">
         <v>42</v>
       </c>
@@ -38921,7 +38929,7 @@
         <v>1</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" s="2" t="n">
         <v>0</v>
@@ -39891,9 +39899,11 @@
         <v>0.01027</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z21" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="Z21" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="AA21" s="7" t="n">
         <v>12</v>
       </c>
@@ -39909,9 +39919,15 @@
       <c r="AE21" s="7" t="n">
         <v>54.5</v>
       </c>
-      <c r="AF21" s="7" t="n"/>
-      <c r="AG21" s="7" t="n"/>
-      <c r="AH21" s="7" t="n"/>
+      <c r="AF21" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG21" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH21" s="7" t="n">
+        <v>74.5</v>
+      </c>
       <c r="AI21" s="7" t="n">
         <v>38</v>
       </c>
@@ -39941,7 +39957,7 @@
         <v>1</v>
       </c>
       <c r="AS21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT21" s="2" t="n">
         <v>0</v>
@@ -40289,9 +40305,11 @@
       </c>
       <c r="X24" s="15" t="n"/>
       <c r="Y24" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z24" s="7" t="n"/>
+        <v>77</v>
+      </c>
+      <c r="Z24" s="7" t="n">
+        <v>22.5</v>
+      </c>
       <c r="AA24" s="7" t="n">
         <v>25</v>
       </c>
@@ -40307,9 +40325,15 @@
       <c r="AE24" s="7" t="n">
         <v>75.75</v>
       </c>
-      <c r="AF24" s="7" t="n"/>
-      <c r="AG24" s="7" t="n"/>
-      <c r="AH24" s="7" t="n"/>
+      <c r="AF24" s="7" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="AG24" s="7" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AH24" s="7" t="n">
+        <v>99.5</v>
+      </c>
       <c r="AI24" s="7" t="n">
         <v>49</v>
       </c>
@@ -40337,7 +40361,7 @@
         <v>1</v>
       </c>
       <c r="AS24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT24" s="2" t="n">
         <v>0</v>
@@ -41325,9 +41349,11 @@
         <v>0.03412</v>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z31" s="7" t="n"/>
+        <v>73</v>
+      </c>
+      <c r="Z31" s="7" t="n">
+        <v>17.5</v>
+      </c>
       <c r="AA31" s="7" t="n">
         <v>18</v>
       </c>
@@ -41343,9 +41369,15 @@
       <c r="AE31" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="AF31" s="7" t="n"/>
-      <c r="AG31" s="7" t="n"/>
-      <c r="AH31" s="7" t="n"/>
+      <c r="AF31" s="7" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="AG31" s="7" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AH31" s="7" t="n">
+        <v>78.75</v>
+      </c>
       <c r="AI31" s="7" t="n">
         <v>29</v>
       </c>
@@ -41377,7 +41409,7 @@
         <v>1</v>
       </c>
       <c r="AS31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT31" s="2" t="n">
         <v>0</v>
@@ -41629,9 +41661,11 @@
         <v>0.00322</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z33" s="7" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Z33" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="AA33" s="7" t="n">
         <v>27.9</v>
       </c>
@@ -41647,9 +41681,15 @@
       <c r="AE33" s="7" t="n">
         <v>76.8</v>
       </c>
-      <c r="AF33" s="7" t="n"/>
-      <c r="AG33" s="7" t="n"/>
-      <c r="AH33" s="7" t="n"/>
+      <c r="AF33" s="7" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="AG33" s="7" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AH33" s="7" t="n">
+        <v>118.05</v>
+      </c>
       <c r="AI33" s="7" t="n">
         <v>38</v>
       </c>
@@ -41673,7 +41713,7 @@
         <v>1</v>
       </c>
       <c r="AS33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT33" s="2" t="n">
         <v>0</v>
@@ -42629,9 +42669,11 @@
         <v>0.0064</v>
       </c>
       <c r="Y40" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z40" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="Z40" s="7" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA40" s="7" t="n">
         <v>9</v>
       </c>
@@ -42647,9 +42689,15 @@
       <c r="AE40" s="7" t="n">
         <v>52.72</v>
       </c>
-      <c r="AF40" s="7" t="n"/>
-      <c r="AG40" s="7" t="n"/>
-      <c r="AH40" s="7" t="n"/>
+      <c r="AF40" s="7" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AG40" s="7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AH40" s="7" t="n">
+        <v>71.47</v>
+      </c>
       <c r="AI40" s="7" t="n">
         <v>38.9</v>
       </c>
@@ -42679,7 +42727,7 @@
         <v>1</v>
       </c>
       <c r="AS40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT40" s="2" t="n">
         <v>0</v>
@@ -42925,9 +42973,11 @@
       </c>
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z42" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="Z42" s="7" t="n">
+        <v>28</v>
+      </c>
       <c r="AA42" s="7" t="n"/>
       <c r="AB42" s="7" t="n">
         <v>38</v>
@@ -42959,7 +43009,7 @@
         <v>1</v>
       </c>
       <c r="AS42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT42" s="2" t="n">
         <v>0</v>
@@ -43185,9 +43235,11 @@
         <v>0.00343</v>
       </c>
       <c r="Y44" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z44" s="7" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="Z44" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="AA44" s="7" t="n">
         <v>12.5</v>
       </c>
@@ -43203,9 +43255,15 @@
       <c r="AE44" s="7" t="n">
         <v>30.25</v>
       </c>
-      <c r="AF44" s="7" t="n"/>
-      <c r="AG44" s="7" t="n"/>
-      <c r="AH44" s="7" t="n"/>
+      <c r="AF44" s="7" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AG44" s="7" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AH44" s="7" t="n">
+        <v>42.25</v>
+      </c>
       <c r="AI44" s="7" t="n"/>
       <c r="AJ44" s="7" t="n">
         <v>18</v>
@@ -43231,7 +43289,7 @@
         <v>1</v>
       </c>
       <c r="AS44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT44" s="2" t="n">
         <v>0</v>
@@ -44703,9 +44761,11 @@
       </c>
       <c r="X55" s="15" t="n"/>
       <c r="Y55" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z55" s="7" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Z55" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="AA55" s="7" t="n">
         <v>7.5</v>
       </c>
@@ -44721,9 +44781,15 @@
       <c r="AE55" s="7" t="n">
         <v>81.5</v>
       </c>
-      <c r="AF55" s="7" t="n"/>
-      <c r="AG55" s="7" t="n"/>
-      <c r="AH55" s="7" t="n"/>
+      <c r="AF55" s="7" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="AG55" s="7" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AH55" s="7" t="n">
+        <v>86.5</v>
+      </c>
       <c r="AI55" s="7" t="n"/>
       <c r="AJ55" s="7" t="n"/>
       <c r="AK55" s="7" t="n"/>
@@ -44743,7 +44809,7 @@
         <v>1</v>
       </c>
       <c r="AS55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT55" s="2" t="n">
         <v>1</v>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_por_grupo.xlsx
@@ -39451,7 +39451,7 @@
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="15" t="n"/>
       <c r="Y18" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z18" s="7" t="n">
         <v>22.5</v>
@@ -39472,13 +39472,13 @@
         <v>75.8</v>
       </c>
       <c r="AF18" s="7" t="n">
-        <v>88.05</v>
+        <v>86.8</v>
       </c>
       <c r="AG18" s="7" t="n">
         <v>95.8</v>
       </c>
       <c r="AH18" s="7" t="n">
-        <v>102.05</v>
+        <v>103.3</v>
       </c>
       <c r="AI18" s="7" t="n"/>
       <c r="AJ18" s="7" t="n"/>
@@ -43531,9 +43531,11 @@
         <v>0.00693</v>
       </c>
       <c r="Y46" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z46" s="7" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="Z46" s="7" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA46" s="7" t="n">
         <v>16</v>
       </c>
@@ -43549,9 +43551,15 @@
       <c r="AE46" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="AF46" s="7" t="n"/>
-      <c r="AG46" s="7" t="n"/>
-      <c r="AH46" s="7" t="n"/>
+      <c r="AF46" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="AG46" s="7" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AH46" s="7" t="n">
+        <v>70.75</v>
+      </c>
       <c r="AI46" s="7" t="n">
         <v>28</v>
       </c>
@@ -43581,7 +43589,7 @@
         <v>1</v>
       </c>
       <c r="AS46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT46" s="2" t="n">
         <v>0</v>
